--- a/Compititor's_Price/IKO_Prices/IKO_Prices_03-04-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_03-04-2026.xlsx
@@ -855,12 +855,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£29.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£29.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£29.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£29.30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -954,27 +954,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.86</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.86</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.84</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.75</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.75</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£31.34</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1125,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£38.11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1182,27 +1182,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£48.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£48.29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£48.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£47.37</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1239,27 +1239,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£47.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£47.37</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£47.37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>£46.78</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Error: [WinError 233] No process is on the other end of the pipe</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
